--- a/Test Plan.xlsx
+++ b/Test Plan.xlsx
@@ -1,24 +1,88 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F62454C-8C94-4FB0-87DD-C0B5AE48673F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCaseTemplate" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={748C7DF5-B8E7-4072-8A47-3C2A2AA56B85}</author>
+    <author>tc={C21A305E-AF8B-40AC-9EAE-8E88B53E649C}</author>
+    <author>tc={2DDF0464-25E4-488C-ACA1-C21B8DBB6F90}</author>
+  </authors>
+  <commentList>
+    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{748C7DF5-B8E7-4072-8A47-3C2A2AA56B85}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    We need tests for every requirement, they need to demonstrate the same functionality stated in use cases</t>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="1" shapeId="0" xr:uid="{C21A305E-AF8B-40AC-9EAE-8E88B53E649C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    We need a total of 10 tests, we should have a mix of non-functional and at least one test for each functional requirement (1-3)</t>
+      </text>
+    </comment>
+    <comment ref="F27" authorId="2" shapeId="0" xr:uid="{2DDF0464-25E4-488C-ACA1-C21B8DBB6F90}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    P0 - Critical
+P1 - Important
+P2 - Minor</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="116">
+  <si>
+    <t>Test Case Template</t>
+  </si>
   <si>
     <t>TestCaseId</t>
   </si>
   <si>
+    <t>RequirementId</t>
+  </si>
+  <si>
+    <t>Requirement Type</t>
+  </si>
+  <si>
     <t>Component</t>
   </si>
   <si>
@@ -28,6 +92,9 @@
     <t>Description/Test Summary</t>
   </si>
   <si>
+    <t>Pre-requisites</t>
+  </si>
+  <si>
     <t>Test Steps</t>
   </si>
   <si>
@@ -43,49 +110,329 @@
     <t>Test Executed By</t>
   </si>
   <si>
-    <t>Test Case Template</t>
-  </si>
-  <si>
-    <t>Pre-requisites</t>
-  </si>
-  <si>
-    <t>GoogleSearch_1</t>
-  </si>
-  <si>
-    <t>Search_Bar_Module</t>
+    <t>TC-001</t>
+  </si>
+  <si>
+    <t>FR-1</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Seat Selection</t>
   </si>
   <si>
     <t>P0</t>
   </si>
   <si>
-    <t>Verify that when a user writes a search term and presses enter, search results should be displayed</t>
-  </si>
-  <si>
-    <t>Browser is launched</t>
-  </si>
-  <si>
-    <t>1. Write the url - http://google.com in the browser's URL bar and press enter.
-2. Once google.com is launched, write the search term - "Apple" in the google search bar.
-3. Press enter.</t>
-  </si>
-  <si>
-    <t>Search results related to 'apple' should be displayed</t>
-  </si>
-  <si>
-    <t>Search results with 'apple' keyword are displayed</t>
+    <t>Verify the system displays real-time seat availability</t>
+  </si>
+  <si>
+    <t>Viewing a movie showtime</t>
+  </si>
+  <si>
+    <t>1. Select a movie and showtime
+2. Open seat selection page</t>
+  </si>
+  <si>
+    <t>Seat map should display reserved, locked, and available seats correctly</t>
+  </si>
+  <si>
+    <t>Seat map displays reserved, locked, and available seats</t>
   </si>
   <si>
     <t>Pass</t>
   </si>
   <si>
-    <t>TesterK</t>
+    <t>REQ_TESTER_FR1</t>
+  </si>
+  <si>
+    <t>TC-002</t>
+  </si>
+  <si>
+    <t>Seat Reservation</t>
+  </si>
+  <si>
+    <t>Verify selected seats lock</t>
+  </si>
+  <si>
+    <t>Seat map is visible</t>
+  </si>
+  <si>
+    <t>1. Select seat A5 
+2. Open seat map on another device</t>
+  </si>
+  <si>
+    <t>Seat map on second device displays that seat A5 is locked</t>
+  </si>
+  <si>
+    <t>Seat A5 changed to locked status immediately</t>
+  </si>
+  <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>Verify seat lock expires after timer</t>
+  </si>
+  <si>
+    <t>Seat A5 locked</t>
+  </si>
+  <si>
+    <t>1. Open seat map on separate device
+2. Wait 10 minutes</t>
+  </si>
+  <si>
+    <t>Seat A5 is available again after 10 minutes</t>
+  </si>
+  <si>
+    <t>Seat A5 is available on seat map</t>
+  </si>
+  <si>
+    <t>TC-004</t>
+  </si>
+  <si>
+    <t>Verify reserved seats are displayed</t>
+  </si>
+  <si>
+    <t>Seat A5 is confirmed</t>
+  </si>
+  <si>
+    <t>1. Open seat map on separate device</t>
+  </si>
+  <si>
+    <t>Seat A5 is reserved on map</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pricing </t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Verify dynamic pricing based on seat location</t>
+  </si>
+  <si>
+    <t>Seat map visible</t>
+  </si>
+  <si>
+    <t>1. Select front row seat
+2. Select center seat</t>
+  </si>
+  <si>
+    <t>Different price tiers displayed</t>
+  </si>
+  <si>
+    <t>Front row price was discounted, while center seat had premium pricing</t>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>Traffic Management</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Verify waiting room appears during high traffic</t>
+  </si>
+  <si>
+    <t>System traffic simulated</t>
+  </si>
+  <si>
+    <t>1. Attempt to access seat selection</t>
+  </si>
+  <si>
+    <t>User placed in queue</t>
+  </si>
+  <si>
+    <t>User is redirected to waiting room page</t>
+  </si>
+  <si>
+    <t>TC-007</t>
+  </si>
+  <si>
+    <t>FR-2</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>Verify payment processing</t>
+  </si>
+  <si>
+    <t>Seats selected</t>
+  </si>
+  <si>
+    <t>1. Enter valid payment
+2. Submit</t>
+  </si>
+  <si>
+    <t>Payment processed and ticket generated</t>
+  </si>
+  <si>
+    <t>Payment approved and ticket generated</t>
+  </si>
+  <si>
+    <t>REQ_TESTER_FR2</t>
+  </si>
+  <si>
+    <t>TC-008</t>
+  </si>
+  <si>
+    <t>Verify failed payment and release seats</t>
+  </si>
+  <si>
+    <t>Seat locked</t>
+  </si>
+  <si>
+    <t>1. Enter invalid card
+2. Submit</t>
+  </si>
+  <si>
+    <t>Transaction fails and seats released</t>
+  </si>
+  <si>
+    <t>Payment declined and seat returned to available</t>
+  </si>
+  <si>
+    <t>TC-009</t>
+  </si>
+  <si>
+    <t>Ticket Generation</t>
+  </si>
+  <si>
+    <t>Verify unique ticket and ID creation</t>
+  </si>
+  <si>
+    <t>Payment completed</t>
+  </si>
+  <si>
+    <t>1. Complete purchase</t>
+  </si>
+  <si>
+    <t>Unique ticket ID generated</t>
+  </si>
+  <si>
+    <t>User was given a unique ticket ID and barcode</t>
+  </si>
+  <si>
+    <t>TC-010</t>
+  </si>
+  <si>
+    <t>Ticket Delivery</t>
+  </si>
+  <si>
+    <t>Verify ticket can be delivered via email and SMS</t>
+  </si>
+  <si>
+    <t>Ticket purchased</t>
+  </si>
+  <si>
+    <t>1. Deliver ticket through email
+2. Deliver ticket thorugh SMS</t>
+  </si>
+  <si>
+    <t>Scannable ticket sent to email and SMS texts</t>
+  </si>
+  <si>
+    <t>User received ticket through email and SMS</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
+    <t>Kiosk</t>
+  </si>
+  <si>
+    <t>TC-012</t>
+  </si>
+  <si>
+    <t>FR-3</t>
+  </si>
+  <si>
+    <t>Concession Menu</t>
+  </si>
+  <si>
+    <t>TC-013</t>
+  </si>
+  <si>
+    <t>Order system</t>
+  </si>
+  <si>
+    <t>TC-014</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>TC-015</t>
+  </si>
+  <si>
+    <t>Age Verification</t>
+  </si>
+  <si>
+    <t>TC-016</t>
+  </si>
+  <si>
+    <t>NFR-Performance</t>
+  </si>
+  <si>
+    <t>Non-functional</t>
+  </si>
+  <si>
+    <t>Checkout</t>
+  </si>
+  <si>
+    <t>TC-017</t>
+  </si>
+  <si>
+    <t>NFR-Security</t>
+  </si>
+  <si>
+    <t>Web Security</t>
+  </si>
+  <si>
+    <t>TC-018</t>
+  </si>
+  <si>
+    <t>NFR-Reliability</t>
+  </si>
+  <si>
+    <t>TC-019</t>
+  </si>
+  <si>
+    <t>NFR-Portability</t>
+  </si>
+  <si>
+    <t>Browser Support</t>
+  </si>
+  <si>
+    <t>TC-020</t>
+  </si>
+  <si>
+    <t>Security
+Constraint</t>
+  </si>
+  <si>
+    <t>Non-functional
+Constraint</t>
+  </si>
+  <si>
+    <t>Ticket Validation</t>
+  </si>
+  <si>
+    <t>Verify ticket can not be scanned twice</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,7 +483,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -159,24 +506,124 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -187,14 +634,23 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Ryann Silverio" id="{6CFCA1E8-42B1-4FFF-ACCB-E6E4E5CE856C}" userId="S::rsilverio5200@sdsu.edu::358ec1cc-2ef4-431f-a5b6-ac18093bd4ef" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -232,7 +688,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -304,7 +760,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -476,106 +932,875 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="O3" dT="2026-03-16T21:45:57.06" personId="{00000000-0000-0000-0000-000000000000}" id="{748C7DF5-B8E7-4072-8A47-3C2A2AA56B85}" done="1">
+    <text>We need tests for every requirement, they need to demonstrate the same functionality stated in use cases</text>
+  </threadedComment>
+  <threadedComment ref="M13" dT="2026-03-19T22:05:05.56" personId="{6CFCA1E8-42B1-4FFF-ACCB-E6E4E5CE856C}" id="{C21A305E-AF8B-40AC-9EAE-8E88B53E649C}">
+    <text>We need a total of 10 tests, we should have a mix of non-functional and at least one test for each functional requirement (1-3)</text>
+  </threadedComment>
+  <threadedComment ref="F27" dT="2026-03-16T21:47:23.35" personId="{00000000-0000-0000-0000-000000000000}" id="{2DDF0464-25E4-488C-ACA1-C21B8DBB6F90}">
+    <text>P0 - Critical
+P1 - Important
+P2 - Minor</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" customWidth="1"/>
-    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.28515625" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" ht="21">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="16"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="L2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:15" ht="90" customHeight="1">
+      <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="E3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="F3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="H3" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
+      <c r="I3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="90" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="90" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="90" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="90" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="90" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="90" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="90" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="90" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="90" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="90" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" ht="90" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" ht="90" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" ht="90" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" ht="90" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" ht="90" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" ht="90" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" ht="90" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" ht="90" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" ht="90" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="27" spans="1:12"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003BA3AC22E708E847AFCC0318E576DEE5" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="efd17050d9e361464a708c1288111774">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f5f6a6c0-12b1-4dba-8712-65d05e8a1efc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ba3187dc71b09c4b99c0c7818f023c0f" ns3:_="">
+    <xsd:import namespace="f5f6a6c0-12b1-4dba-8712-65d05e8a1efc"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f5f6a6c0-12b1-4dba-8712-65d05e8a1efc" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FC93312-9167-4635-BCA1-C00A9CA7D5CF}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85132BC6-E6D1-4D65-9C02-CF427B83DA43}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68F4D7D-89F0-423B-89C4-16FF93914CB6}"/>
 </file>
--- a/Test Plan.xlsx
+++ b/Test Plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F62454C-8C94-4FB0-87DD-C0B5AE48673F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B57104D0-8A38-479A-9962-4573B9FBC8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,12 +33,25 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={A90BF4AC-3992-45E8-AFEB-5A2C929D9743}</author>
     <author>tc={748C7DF5-B8E7-4072-8A47-3C2A2AA56B85}</author>
     <author>tc={C21A305E-AF8B-40AC-9EAE-8E88B53E649C}</author>
     <author>tc={2DDF0464-25E4-488C-ACA1-C21B8DBB6F90}</author>
   </authors>
   <commentList>
-    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{748C7DF5-B8E7-4072-8A47-3C2A2AA56B85}">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{A90BF4AC-3992-45E8-AFEB-5A2C929D9743}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Test Plan Requirements:
+10 test cases
+at least 2 test cases for unit, functional, system tests
+Reply:
+    2 unit tests and 2 system tests are found at bottom</t>
+      </text>
+    </comment>
+    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{748C7DF5-B8E7-4072-8A47-3C2A2AA56B85}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -46,15 +59,17 @@
     We need tests for every requirement, they need to demonstrate the same functionality stated in use cases</t>
       </text>
     </comment>
-    <comment ref="M13" authorId="1" shapeId="0" xr:uid="{C21A305E-AF8B-40AC-9EAE-8E88B53E649C}">
+    <comment ref="M13" authorId="2" shapeId="0" xr:uid="{C21A305E-AF8B-40AC-9EAE-8E88B53E649C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    We need a total of 10 tests, we should have a mix of non-functional and at least one test for each functional requirement (1-3)</t>
+    We need a total of 10 tests, we should have a mix of non-functional and at least one test for each functional requirement (1-3)
+Reply:
+    we need 3 for unit and system test cases</t>
       </text>
     </comment>
-    <comment ref="F27" authorId="2" shapeId="0" xr:uid="{2DDF0464-25E4-488C-ACA1-C21B8DBB6F90}">
+    <comment ref="F27" authorId="3" shapeId="0" xr:uid="{2DDF0464-25E4-488C-ACA1-C21B8DBB6F90}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -69,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="145">
   <si>
     <t>Test Case Template</t>
   </si>
@@ -426,13 +441,109 @@
   </si>
   <si>
     <t>Verify ticket can not be scanned twice</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>LockSeat</t>
+  </si>
+  <si>
+    <t>Lock seat when it has already been selected by another user</t>
+  </si>
+  <si>
+    <t>Viewing seat availability</t>
+  </si>
+  <si>
+    <t>1. Seat selected by another user
+2. Try to select seat that was just selected</t>
+  </si>
+  <si>
+    <t>Selected seat is locked from other users</t>
+  </si>
+  <si>
+    <t>Correct seat is locked and cannot be selected by other users</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>UpdateAvailability</t>
+  </si>
+  <si>
+    <t>Verify that the UpdateAvailability works correctly, updating seat status after a seat is locked, purchased, or released.</t>
+  </si>
+  <si>
+    <t>A valid movie and showtime exist
+A seat is available
+Seat map is loaded</t>
+  </si>
+  <si>
+    <t>1. Lock seat
+2. Complete purchase or release seat
+3. Refresh seat map</t>
+  </si>
+  <si>
+    <t>Seat status updates correctly after each action</t>
+  </si>
+  <si>
+    <t>Seat map reflects correct availability</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>End to End Concession Purchase</t>
+  </si>
+  <si>
+    <t>Verify full concession order flow works correctly.</t>
+  </si>
+  <si>
+    <t>Valid ticket, items available</t>
+  </si>
+  <si>
+    <t>1. Select items
+2. Submit order
+3. Check staff dashboard</t>
+  </si>
+  <si>
+    <t>Order is processed, linked to seat, and sent to staff</t>
+  </si>
+  <si>
+    <t>Order completed and visible to staff</t>
+  </si>
+  <si>
+    <t>TC-024</t>
+  </si>
+  <si>
+    <t>Create Login</t>
+  </si>
+  <si>
+    <t>Verify new user can create an account login and use it to view movies</t>
+  </si>
+  <si>
+    <t>New user selects create account on website</t>
+  </si>
+  <si>
+    <t>1. Create account
+2. Log in
+3. Access account page</t>
+  </si>
+  <si>
+    <t>Account created and login successful</t>
+  </si>
+  <si>
+    <t>User logged in and accessed account features</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -461,6 +572,17 @@
       <color rgb="FF333333"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Verdana"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Verdana"/>
     </font>
   </fonts>
   <fills count="4">
@@ -588,7 +710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -615,6 +737,15 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -639,12 +770,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Ryann Silverio" id="{6CFCA1E8-42B1-4FFF-ACCB-E6E4E5CE856C}" userId="S::rsilverio5200@sdsu.edu::358ec1cc-2ef4-431f-a5b6-ac18093bd4ef" providerId="AD"/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -934,11 +1059,22 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="M3" dT="2026-03-20T00:30:19.09" personId="{00000000-0000-0000-0000-000000000000}" id="{A90BF4AC-3992-45E8-AFEB-5A2C929D9743}">
+    <text>Test Plan Requirements:
+10 test cases
+at least 2 test cases for unit, functional, system tests</text>
+  </threadedComment>
+  <threadedComment ref="M3" dT="2026-03-20T00:32:10.63" personId="{00000000-0000-0000-0000-000000000000}" id="{B3680025-3553-43BA-940A-7601695F2A83}" parentId="{A90BF4AC-3992-45E8-AFEB-5A2C929D9743}">
+    <text>2 unit tests and 2 system tests are found at bottom</text>
+  </threadedComment>
   <threadedComment ref="O3" dT="2026-03-16T21:45:57.06" personId="{00000000-0000-0000-0000-000000000000}" id="{748C7DF5-B8E7-4072-8A47-3C2A2AA56B85}" done="1">
     <text>We need tests for every requirement, they need to demonstrate the same functionality stated in use cases</text>
   </threadedComment>
-  <threadedComment ref="M13" dT="2026-03-19T22:05:05.56" personId="{6CFCA1E8-42B1-4FFF-ACCB-E6E4E5CE856C}" id="{C21A305E-AF8B-40AC-9EAE-8E88B53E649C}">
+  <threadedComment ref="M13" dT="2026-03-19T22:05:05.56" personId="{00000000-0000-0000-0000-000000000000}" id="{C21A305E-AF8B-40AC-9EAE-8E88B53E649C}">
     <text>We need a total of 10 tests, we should have a mix of non-functional and at least one test for each functional requirement (1-3)</text>
+  </threadedComment>
+  <threadedComment ref="M13" dT="2026-03-19T23:47:46.18" personId="{00000000-0000-0000-0000-000000000000}" id="{55DD8FFC-4F01-4A81-93C6-0A6D70F8B13E}" parentId="{C21A305E-AF8B-40AC-9EAE-8E88B53E649C}">
+    <text>we need 3 for unit and system test cases</text>
   </threadedComment>
   <threadedComment ref="F27" dT="2026-03-16T21:47:23.35" personId="{00000000-0000-0000-0000-000000000000}" id="{2DDF0464-25E4-488C-ACA1-C21B8DBB6F90}">
     <text>P0 - Critical
@@ -956,7 +1092,7 @@
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.85546875" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.28515625" customWidth="1"/>
     <col min="5" max="5" width="7.42578125" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -968,20 +1104,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
@@ -1622,6 +1758,158 @@
       <c r="J22" s="3"/>
       <c r="K22" s="5"/>
       <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" ht="69" customHeight="1">
+      <c r="A23" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="93.75" customHeight="1">
+      <c r="A24" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="63.75" customHeight="1">
+      <c r="A25" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="55.5" customHeight="1">
+      <c r="A26" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="27" spans="1:12"/>
   </sheetData>
@@ -1635,6 +1923,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003BA3AC22E708E847AFCC0318E576DEE5" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="efd17050d9e361464a708c1288111774">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f5f6a6c0-12b1-4dba-8712-65d05e8a1efc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ba3187dc71b09c4b99c0c7818f023c0f" ns3:_="">
     <xsd:import namespace="f5f6a6c0-12b1-4dba-8712-65d05e8a1efc"/>
@@ -1778,7 +2072,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1787,20 +2081,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68F4D7D-89F0-423B-89C4-16FF93914CB6}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FC93312-9167-4635-BCA1-C00A9CA7D5CF}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85132BC6-E6D1-4D65-9C02-CF427B83DA43}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68F4D7D-89F0-423B-89C4-16FF93914CB6}"/>
 </file>
--- a/Test Plan.xlsx
+++ b/Test Plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA88DA0E-5015-4D04-82AF-23DCA72D2773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C8F75B8-7CBF-417D-8C80-57F3537A5F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="94">
   <si>
-    <t>Test Case Template</t>
+    <t>Test Case Table - CinemaCore Systems</t>
   </si>
   <si>
     <t>TestCaseId</t>
@@ -748,6 +748,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -1189,18 +1192,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1348,11 +1351,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68F4D7D-89F0-423B-89C4-16FF93914CB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85132BC6-E6D1-4D65-9C02-CF427B83DA43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85132BC6-E6D1-4D65-9C02-CF427B83DA43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68F4D7D-89F0-423B-89C4-16FF93914CB6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
